--- a/output/reports/cv_experiment_Bagging_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>37.76048135757446</v>
+        <v>0.8247137069702148</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8825712016553097</v>
+        <v>0.9951186213925265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8978971370661262</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.897097208156062</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9600591815330886</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>73.87733936309814</v>
+        <v>1.429044008255005</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8872486501526529</v>
+        <v>0.991859371617992</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8978971370661262</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.897097208156062</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9600591815330886</v>
+        <v>0.9989818428644154</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>37.76048135757446</v>
+        <v>0.8247137069702148</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8825712016553097</v>
+        <v>0.9951186213925265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8978971370661262</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.897097208156062</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9600591815330886</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>73.87733936309814</v>
+        <v>1.429044008255005</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8872486501526529</v>
+        <v>0.991859371617992</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8978971370661262</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.897097208156062</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9600591815330886</v>
+        <v>0.9989818428644154</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_Bagging_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8247137069702148</v>
+        <v>1.793247222900391</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9951186213925265</v>
+        <v>0.6218871679987316</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.7584745762711864</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.732381284105422</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9994909214322077</v>
+        <v>0.9126059322033898</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.8, 'max_features': 0.8}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.429044008255005</v>
+        <v>3.039506673812866</v>
       </c>
       <c r="E3" t="n">
-        <v>0.991859371617992</v>
+        <v>0.6666699871954733</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.7584745762711864</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.7440459011887585</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9989818428644154</v>
+        <v>0.9085347242171788</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8247137069702148</v>
+        <v>1.793247222900391</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9951186213925265</v>
+        <v>0.6218871679987316</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.7584745762711864</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.732381284105422</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9994909214322077</v>
+        <v>0.9126059322033898</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.8, 'max_features': 0.8}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.429044008255005</v>
+        <v>3.039506673812866</v>
       </c>
       <c r="E3" t="n">
-        <v>0.991859371617992</v>
+        <v>0.6666699871954733</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.7584745762711864</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.7440459011887585</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9989818428644154</v>
+        <v>0.9085347242171788</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
